--- a/data/情景交代.xlsx
+++ b/data/情景交代.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="171" uniqueCount="105">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="347" uniqueCount="211">
   <si>
     <t>疾病</t>
   </si>
@@ -342,6 +342,324 @@
   </si>
   <si>
     <t>患者行颈椎肿瘤切除内固定+肋骨肿瘤切除术，术后症状好转。病理确诊肺来源转移性腺癌。家属咨询后续治疗方案。请你向家属解释后续治疗（化疗、靶向等）及预后。</t>
+  </si>
+  <si>
+    <t>“脑中风的警报”</t>
+  </si>
+  <si>
+    <t>张大爷，68岁，有高血压史，晨起突然出现右侧肢体无力、麻木，言语不清，口角左偏。急诊头颅CT未见出血，考虑急性缺血性脑卒中。你是接诊医生，请开始问诊。</t>
+  </si>
+  <si>
+    <t>患者入院后血压160/95mmHg，NIHSS评分8分，MRI示左侧大脑中动脉供血区急性梗死。需尽快评估溶栓或取栓治疗。请你向家属解释病情及治疗选择。</t>
+  </si>
+  <si>
+    <t>患者错过溶栓时间窗，给予抗血小板、降脂、康复治疗。病情稳定但右侧肢体肌力仍3级，需长期二级预防。请你向患者及家属说明后续治疗及康复计划。</t>
+  </si>
+  <si>
+    <t>出院前患者右侧肢体肌力恢复至4级，言语清晰。需指导二级预防药物（阿司匹林、他汀）、生活方式调整及定期随访。请你进行出院宣教。</t>
+  </si>
+  <si>
+    <t>“半身风云”</t>
+  </si>
+  <si>
+    <t>“惊厥之舞”</t>
+  </si>
+  <si>
+    <t>小王，25岁，2小时前在办公室突然意识丧失、倒地、四肢抽搐、口吐白沫，持续约3分钟后自行停止，醒后对发作无记忆。同事呼叫120送诊。既往体健。你是接诊医生，请开始问诊。</t>
+  </si>
+  <si>
+    <t>患者入院后生命体征平稳，神经系统检查无异常。脑电图示双侧额区棘慢波发放。头颅MRI未见异常。诊断为癫痫（全身性发作）。需开始抗癫痫治疗。请你向患者解释病情。</t>
+  </si>
+  <si>
+    <t>给予丙戊酸钠治疗后，患者未再发作，但出现轻微嗜睡。需调整剂量并监测血药浓度。请你向患者说明药物副作用及注意事项。</t>
+  </si>
+  <si>
+    <t>患者病情控制良好，准备出院。需指导长期用药、避免诱因、定期复查脑电图及肝功能。请你进行出院宣教。</t>
+  </si>
+  <si>
+    <t>“隐形的枷锁”</t>
+  </si>
+  <si>
+    <t>李女士，35岁，近3个月来情绪低落、兴趣减退、失眠、食欲下降，自觉乏力，有自杀念头，由家属陪同就诊。查体无异常。PHQ-9评分18分。你是接诊医生，请开始问诊。</t>
+  </si>
+  <si>
+    <t>患者诊断为中度抑郁发作，建议抗抑郁药物治疗联合心理治疗。家属担心药物副作用及依赖性。请你向患者及家属解释病情及治疗选择。</t>
+  </si>
+  <si>
+    <t>给予舍曲林治疗2周后，患者情绪稍好转，但仍睡眠差，出现恶心。需调整方案。请你向患者说明药物起效时间及副作用处理。</t>
+  </si>
+  <si>
+    <t>治疗8周后，患者情绪明显改善，自杀念头消失，准备出院。需指导继续服药、心理治疗及预防复发。请你进行出院宣教。</t>
+  </si>
+  <si>
+    <t>“心弦紧绷”</t>
+  </si>
+  <si>
+    <t>赵先生，58岁，公司高管，近1周反复出现胸骨后压榨性疼痛，向左肩放射，每次持续5-10分钟，劳累或情绪激动时诱发，休息或含服硝酸甘油可缓解。既往高血压、高血脂史。你是接诊医生，请开始问诊。</t>
+  </si>
+  <si>
+    <t>患者入院后心电图示ST段压低，心肌酶正常。考虑不稳定心绞痛，需行冠脉造影评估。家属担心手术风险。请你向患者及家属解释病情及治疗选择。</t>
+  </si>
+  <si>
+    <t>冠脉造影示前降支中段狭窄85%，植入支架1枚，术后胸痛消失。需指导双抗治疗及二级预防。请你向患者说明术后注意事项。</t>
+  </si>
+  <si>
+    <t>患者出院前无胸痛发作，需指导长期用药（阿司匹林、氯吡格雷、他汀）、生活方式调整及定期随访。请你进行出院宣教。</t>
+  </si>
+  <si>
+    <t>“心跳乱了”</t>
+  </si>
+  <si>
+    <t>陈大爷，72岁，退休工人，1小时前突感心悸、胸闷、气短，伴头晕，无胸痛。急诊心电图示快速房颤，心室率150次/分。既往高血压史。你是接诊医生，请开始问诊。</t>
+  </si>
+  <si>
+    <t>患者入院后血压130/80mmHg，心室率120次/分，予胺碘酮复律及抗凝治疗。需评估卒中风险（CHA2DS2-VASc评分）及出血风险（HAS-BLED评分）。请你向患者及家属解释病情及治疗选择。</t>
+  </si>
+  <si>
+    <t>患者转复为窦性心律，心室率70次/分。需长期抗凝预防卒中，选择华法林或NOAC。请你向患者说明抗凝治疗的必要性及注意事项。</t>
+  </si>
+  <si>
+    <t>出院前患者病情稳定，需指导长期抗凝、定期监测INR（若用华法林）、控制心率及预防复发。请你进行出院宣教。</t>
+  </si>
+  <si>
+    <t>“泵的挣扎”</t>
+  </si>
+  <si>
+    <t>吴大爷，76岁，有冠心病史，3天前受凉后咳嗽、咳痰，今晨突发严重呼吸困难、端坐呼吸、咳粉红色泡沫样痰。急诊血压210/110mmHg，双肺满布湿啰音。你是接诊医生，请开始问诊。</t>
+  </si>
+  <si>
+    <t>患者入院后诊断为急性左心衰，给予吸氧、利尿、扩血管、强心治疗后症状缓解。需明确病因及评估心功能。请你向患者及家属解释病情及治疗。</t>
+  </si>
+  <si>
+    <t>心脏超声示左室射血分数35%，左室扩大，考虑缺血性心肌病。需长期药物治疗及心衰管理。请你向患者说明长期治疗方案。</t>
+  </si>
+  <si>
+    <t>出院前患者病情稳定，心功能Ⅱ级，需指导长期用药（ACEI/ARB、β阻滞剂、利尿剂）、限盐限水、监测体重及定期随访。请你进行出院宣教。</t>
+  </si>
+  <si>
+    <t>“喘息的风箱”</t>
+  </si>
+  <si>
+    <t>小刘，25岁，程序员，2小时前加班时突然发作性呼吸困难、喘息、胸闷，伴咳嗽，端坐呼吸，自述有过敏性鼻炎史。急诊查体双肺满布哮鸣音。你是接诊医生，请开始问诊。</t>
+  </si>
+  <si>
+    <t>患者入院后予吸氧、雾化吸入β2受体激动剂及糖皮质激素，症状缓解。需进一步明确过敏原及哮喘控制水平。请你向患者解释病情及长期治疗计划。</t>
+  </si>
+  <si>
+    <t>患者肺功能检查示FEV1/FVC&lt;70%，支气管舒张试验阳性，确诊支气管哮喘。需长期吸入激素控制气道炎症。请你向患者说明用药注意事项。</t>
+  </si>
+  <si>
+    <t>患者症状控制良好，准备出院。需指导规律用药、峰流速监测、避免诱因及定期复查。请你进行出院宣教。</t>
+  </si>
+  <si>
+    <t>“被困的气泡”</t>
+  </si>
+  <si>
+    <t>小张，22岁，大学生，打篮球时突然右侧胸痛、呼吸困难，呈针刺样疼痛，深吸气加重。既往体健。急诊查体右肺呼吸音消失。你是接诊医生，请开始问诊。</t>
+  </si>
+  <si>
+    <t>患者入院后胸部X线示右侧气胸，肺压缩约40%。需行胸腔闭式引流。患者害怕手术。请你向患者解释病情及治疗必要性。</t>
+  </si>
+  <si>
+    <t>行胸腔闭式引流后，症状缓解，引流管在位。需观察有无漏气及肺复张情况。请你向患者说明术后注意事项。</t>
+  </si>
+  <si>
+    <t>拔管后复查X线示肺完全复张，准备出院。需指导避免剧烈运动、潜水及乘飞机，预防复发。请你进行出院宣教。</t>
+  </si>
+  <si>
+    <t>“沉默的阴影”</t>
+  </si>
+  <si>
+    <t>老李，65岁，退休工人，长期吸烟（40包年），近3个月出现刺激性干咳、痰中带血丝，伴消瘦、乏力。胸部X线示右肺门肿块影。你是接诊医生，请开始问诊。</t>
+  </si>
+  <si>
+    <t>患者入院后胸部CT示右肺上叶占位，伴纵隔淋巴结肿大。支气管镜活检病理回报：肺鳞癌。需进一步分期及制定治疗方案。请你向患者及家属解释病情。</t>
+  </si>
+  <si>
+    <t>患者经PET-CT评估为ⅢA期（N2），建议新辅助化疗后手术，或同步放化疗。家属犹豫不决。请你向家属解释不同治疗方案的利弊。</t>
+  </si>
+  <si>
+    <t>患者选择新辅助化疗后手术，术后恢复良好，准备出院。需指导定期复查、戒烟及康复。请你进行出院宣教。</t>
+  </si>
+  <si>
+    <t>“胃里的火山”</t>
+  </si>
+  <si>
+    <t>赵先生，38岁，销售经理，工作压力大，饮食不规律，近2月上腹痛反复发作，饥饿时明显，夜间常痛醒。来门诊就诊。你是接诊医生，请开始问诊。</t>
+  </si>
+  <si>
+    <t>患者胃镜结果示十二指肠球部溃疡，活检良性，幽门螺杆菌阳性。医生建议住院抗Hp治疗，患者担心影响工作，犹豫不决。请你向患者解释病情及治疗必要性。</t>
+  </si>
+  <si>
+    <t>患者完成2周抗Hp治疗及4周抑酸治疗，症状消失，复查胃镜示溃疡缩小但未完全愈合，Hp转阴。询问后续治疗。请分析原因并调整方案。</t>
+  </si>
+  <si>
+    <t>患者溃疡完全愈合，准备出院。需要交代后续治疗、康复和预防措施。请你给出综合建议。</t>
+  </si>
+  <si>
+    <t>“肝胆风云”</t>
+  </si>
+  <si>
+    <t>王阿姨，52岁，体型偏胖，喜食油腻。2天前婚宴后突发右上腹剧痛，向右肩放射，伴恶心呕吐。急诊就诊。你是接诊医生，请开始问诊。</t>
+  </si>
+  <si>
+    <t>患者经抗感染、解痉治疗后症状缓解，但B超仍见胆囊结石。医生建议择期手术，患者犹豫不决。请你向患者解释手术必要性及时机。</t>
+  </si>
+  <si>
+    <t>患者行腹腔镜胆囊切除术后出现腹痛、发热、黄疸，诊断为胆总管残余结石，需行ERCP取石。患者情绪紧张，需解释病情。</t>
+  </si>
+  <si>
+    <t>患者行ERCP取石后恢复良好，准备出院。需要交代后续饮食和预防措施。请你进行出院宣教。</t>
+  </si>
+  <si>
+    <t>“肠路惊魂”</t>
+  </si>
+  <si>
+    <t>陈大爷，68岁，退休工人，近3月排便习惯改变，便秘与腹泻交替，大便带血，血色暗红，里急后重感，体重下降约5kg。来门诊就诊。你是接诊医生，请开始问诊。</t>
+  </si>
+  <si>
+    <t>患者住院后完善检查，确诊为直肠癌Ⅲ期。医生建议手术+辅助治疗。患者及家属十分担心，需沟通病情。</t>
+  </si>
+  <si>
+    <t>患者行直肠癌低位前切除术，术后病理证实淋巴结转移，需行辅助化疗。患者对化疗恐惧，需解释化疗目的和注意事项。</t>
+  </si>
+  <si>
+    <t>患者完成辅助化疗，恢复良好。准备出院，进行长期随访指导。请你进行出院宣教。</t>
+  </si>
+  <si>
+    <t>“石破天惊”</t>
+  </si>
+  <si>
+    <t>李先生，45岁，建筑工人，1小时前突发右腰腹部绞痛，向下腹部及会阴部放射，伴恶心呕吐，大汗淋漓。痛苦面容，辗转不安。你是接诊医生，请开始问诊。</t>
+  </si>
+  <si>
+    <t>患者经解痉止痛后疼痛缓解，尿常规示红细胞满视野，腹部X线平片示右输尿管中段约0.8cm阳性结石。医生建议ESWL，患者担心费用和效果。请你向患者解释病情及治疗选择。</t>
+  </si>
+  <si>
+    <t>患者ESWL术后1周复查结石无变化，仍有间断腰痛。医生建议行输尿管镜碎石，患者害怕再次手术。请你解释输尿管镜的必要性和优势。</t>
+  </si>
+  <si>
+    <t>患者行输尿管镜碎石成功，结石清除，恢复良好。准备出院，咨询长期预防措施。请你进行出院宣教。</t>
+  </si>
+  <si>
+    <t>“隐秘的河流”</t>
+  </si>
+  <si>
+    <t>张女士，38岁，公司职员，近2月双下肢水肿，尿泡沫增多，伴乏力、腰酸。门诊查体血压150/95mmHg，双下肢轻度水肿。你是接诊医生，请开始问诊。</t>
+  </si>
+  <si>
+    <t>患者住院后检查：尿蛋白1.5g/24h，镜下血尿，血肌酐105μmol/L，eGFR 65ml/min，免疫学阴性。诊断为慢性肾小球肾炎。医生建议长期ACEI治疗，患者担心终身服药和预后。请你解释病情及治疗计划。</t>
+  </si>
+  <si>
+    <t>患者坚持服药半年，血压控制可，但血肌酐升至130μmol/L，eGFR 50ml/min，蛋白尿0.8g/24h。患者情绪低落，担心肾衰竭。请分析原因并调整方案。</t>
+  </si>
+  <si>
+    <t>患者5年后随访，eGFR降至35ml/min，出现贫血、血磷升高，需准备替代治疗。请你与患者沟通长期管理方向。</t>
+  </si>
+  <si>
+    <t>“火海警报”</t>
+  </si>
+  <si>
+    <t>王女士，28岁，教师，2天前劳累后出现尿频、尿急、尿痛，今晨寒战、高热（39.2℃），伴右侧腰痛、恶心。急诊就诊。你是接诊医生，请开始问诊。</t>
+  </si>
+  <si>
+    <t>患者入院后尿培养示大肠埃希菌，药敏敏感。经抗生素治疗后体温下降，但仍有腰痛。B超示右肾轻度积水，CT示右输尿管中段结石。医生建议控制感染后处理结石，患者害怕手术。请你解释处理原则。</t>
+  </si>
+  <si>
+    <t>患者感染控制后，行输尿管镜碎石取石术，手术顺利。术后恢复良好，咨询出院后如何预防感染和结石复发。请你进行出院宣教。</t>
+  </si>
+  <si>
+    <t>患者术后恢复良好，准备出院。需要交代后续预防措施。请你给出综合建议。</t>
+  </si>
+  <si>
+    <t>“折翼天使”</t>
+  </si>
+  <si>
+    <t>小明，7岁，课间玩耍从单杠摔下，右手撑地，右肘部肿胀、剧痛，不敢活动。由老师陪同来急诊。你是接诊医生，请开始问诊。</t>
+  </si>
+  <si>
+    <t>患儿X线片示右肱骨髁上骨折，骨折端明显移位，且出现张力性水疱，桡动脉搏动减弱。需急诊手术。家长十分担心，请你解释病情及手术必要性。</t>
+  </si>
+  <si>
+    <t>患儿术后出现前臂剧痛，被动伸指时加重，桡动脉搏动消失，手部苍白、麻木，考虑骨筋膜室综合征，需紧急切开减压。请你向家长解释病情及紧急处理方案。</t>
+  </si>
+  <si>
+    <t>患儿经减压后恢复良好，准备出院。需要交代后续康复和预防措施。请你给出综合建议。</t>
+  </si>
+  <si>
+    <t>“行走的齿轮”</t>
+  </si>
+  <si>
+    <t>李奶奶，68岁，双膝疼痛5年，上下楼梯困难，晨僵&lt;30分钟。门诊就诊。你是接诊医生，请开始问诊。</t>
+  </si>
+  <si>
+    <t>患者X线示双膝骨关节炎表现。经保守治疗效果不理想，咨询进一步方案。请你解释病情及治疗选择。</t>
+  </si>
+  <si>
+    <t>患者疼痛进行性加重，需扶拐行走，决定行右膝人工关节置换。请你向患者及家属解释手术方案、风险及术后康复。</t>
+  </si>
+  <si>
+    <t>患者行右人工膝关节置换术后恢复顺利，准备出院。需要交代后续康复和长期管理。请你进行出院宣教。</t>
+  </si>
+  <si>
+    <t>“断桥残雪”</t>
+  </si>
+  <si>
+    <t>张先生，35岁，程序员，弯腰搬重物后突发腰痛伴右下肢放射痛，咳嗽加重。门诊就诊。你是接诊医生，请开始问诊。</t>
+  </si>
+  <si>
+    <t>患者MRI示L5-S1椎间盘突出，严格卧床4周效果不佳，咨询后续治疗。请你解释病情及治疗选择。</t>
+  </si>
+  <si>
+    <t>患者出现排尿困难、会阴麻木，考虑马尾综合征，需急诊手术。请你向家属解释病情及紧急手术的必要性。</t>
+  </si>
+  <si>
+    <t>患者行急诊髓核摘除术后恢复良好，准备出院。需要交代后续康复和预防复发措施。请你进行出院宣教。</t>
+  </si>
+  <si>
+    <t>“糖衣炮弹”</t>
+  </si>
+  <si>
+    <t>张先生，45岁，公司经理，近2月口渴多饮、多尿、消瘦，有高血压史，父亲患糖尿病。门诊就诊。你是接诊医生，请开始问诊。</t>
+  </si>
+  <si>
+    <t>患者入院后检查确诊2型糖尿病，胰岛素抵抗明显。医生建议二甲双胍治疗，患者担心副作用。请你向患者解释病情及治疗计划。</t>
+  </si>
+  <si>
+    <t>患者服用二甲双胍后出现恶心、腹泻，自行停药，血糖升高。需调整治疗方案。请你向患者解释副作用处理及替代选择。</t>
+  </si>
+  <si>
+    <t>患者更换方案后血糖控制平稳，准备出院。需要交代后续管理措施。请你给出综合建议。</t>
+  </si>
+  <si>
+    <t>“隐形狂飙”</t>
+  </si>
+  <si>
+    <t>李女士，32岁，教师，近3月心慌、手抖、怕热多汗，消瘦，脾气急躁，颈部增粗。门诊就诊。你是接诊医生，请开始问诊。</t>
+  </si>
+  <si>
+    <t>患者确诊Graves病，开始服用甲巯咪唑。需要向患者解释药物注意事项及定期复查的重要性。请你进行用药指导。</t>
+  </si>
+  <si>
+    <t>患者服药后出现咽痛、发热，血常规示粒细胞缺乏，需紧急处理。请你向患者解释病情及治疗调整。</t>
+  </si>
+  <si>
+    <t>患者经治疗后恢复良好，准备出院。需要交代后续用药、监测和预防复发。请你进行出院宣教。</t>
+  </si>
+  <si>
+    <t>“荷尔蒙迷航”</t>
+  </si>
+  <si>
+    <t>王小姐，26岁，因结婚2年未孕就诊。月经稀发，多毛、痤疮，肥胖。门诊就诊。你是接诊医生，请开始问诊。</t>
+  </si>
+  <si>
+    <t>患者确诊多囊卵巢综合征，存在胰岛素抵抗。医生建议生活方式干预+二甲双胍治疗。请你向患者解释病情及治疗计划。</t>
+  </si>
+  <si>
+    <t>患者基础治疗后体重下降，但月经仍不规律，希望怀孕。需讨论促排卵方案。请你向患者解释促排卵治疗的选择和风险。</t>
+  </si>
+  <si>
+    <t>患者成功怀孕，准备从生殖中心转产科随访。需要交代孕期注意事项。请你进行转科前指导。</t>
   </si>
 </sst>
 </file>
@@ -1486,7 +1804,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:C85"/>
+  <dimension ref="A1:C173"/>
   <sheetFormatPr defaultColWidth="9.02654867256637" defaultRowHeight="13.5" outlineLevelCol="2"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -2424,6 +2742,974 @@
         <v>104</v>
       </c>
     </row>
+    <row r="86" spans="1:3">
+      <c r="A86" t="s">
+        <v>105</v>
+      </c>
+      <c r="B86">
+        <v>1</v>
+      </c>
+      <c r="C86" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="87" spans="1:3">
+      <c r="A87" t="s">
+        <v>105</v>
+      </c>
+      <c r="B87">
+        <v>2</v>
+      </c>
+      <c r="C87" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="88" spans="1:3">
+      <c r="A88" t="s">
+        <v>105</v>
+      </c>
+      <c r="B88">
+        <v>3</v>
+      </c>
+      <c r="C88" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="89" spans="1:3">
+      <c r="A89" t="s">
+        <v>105</v>
+      </c>
+      <c r="B89">
+        <v>4</v>
+      </c>
+      <c r="C89" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="90" spans="1:3">
+      <c r="A90" t="s">
+        <v>110</v>
+      </c>
+      <c r="B90">
+        <v>1</v>
+      </c>
+      <c r="C90" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="91" spans="1:3">
+      <c r="A91" t="s">
+        <v>110</v>
+      </c>
+      <c r="B91">
+        <v>2</v>
+      </c>
+      <c r="C91" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="92" spans="1:3">
+      <c r="A92" t="s">
+        <v>110</v>
+      </c>
+      <c r="B92">
+        <v>3</v>
+      </c>
+      <c r="C92" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="93" spans="1:3">
+      <c r="A93" t="s">
+        <v>110</v>
+      </c>
+      <c r="B93">
+        <v>4</v>
+      </c>
+      <c r="C93" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="94" spans="1:3">
+      <c r="A94" t="s">
+        <v>111</v>
+      </c>
+      <c r="B94">
+        <v>1</v>
+      </c>
+      <c r="C94" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="95" spans="1:3">
+      <c r="A95" t="s">
+        <v>111</v>
+      </c>
+      <c r="B95">
+        <v>2</v>
+      </c>
+      <c r="C95" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="96" spans="1:3">
+      <c r="A96" t="s">
+        <v>111</v>
+      </c>
+      <c r="B96">
+        <v>3</v>
+      </c>
+      <c r="C96" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="97" spans="1:3">
+      <c r="A97" t="s">
+        <v>111</v>
+      </c>
+      <c r="B97">
+        <v>4</v>
+      </c>
+      <c r="C97" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="98" spans="1:3">
+      <c r="A98" t="s">
+        <v>116</v>
+      </c>
+      <c r="B98">
+        <v>1</v>
+      </c>
+      <c r="C98" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="99" spans="1:3">
+      <c r="A99" t="s">
+        <v>116</v>
+      </c>
+      <c r="B99">
+        <v>2</v>
+      </c>
+      <c r="C99" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="100" spans="1:3">
+      <c r="A100" t="s">
+        <v>116</v>
+      </c>
+      <c r="B100">
+        <v>3</v>
+      </c>
+      <c r="C100" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="101" spans="1:3">
+      <c r="A101" t="s">
+        <v>116</v>
+      </c>
+      <c r="B101">
+        <v>4</v>
+      </c>
+      <c r="C101" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="102" spans="1:3">
+      <c r="A102" t="s">
+        <v>121</v>
+      </c>
+      <c r="B102">
+        <v>1</v>
+      </c>
+      <c r="C102" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="103" spans="1:3">
+      <c r="A103" t="s">
+        <v>121</v>
+      </c>
+      <c r="B103">
+        <v>2</v>
+      </c>
+      <c r="C103" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="104" spans="1:3">
+      <c r="A104" t="s">
+        <v>121</v>
+      </c>
+      <c r="B104">
+        <v>3</v>
+      </c>
+      <c r="C104" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="105" spans="1:3">
+      <c r="A105" t="s">
+        <v>121</v>
+      </c>
+      <c r="B105">
+        <v>4</v>
+      </c>
+      <c r="C105" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="106" spans="1:3">
+      <c r="A106" t="s">
+        <v>126</v>
+      </c>
+      <c r="B106">
+        <v>1</v>
+      </c>
+      <c r="C106" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="107" spans="1:3">
+      <c r="A107" t="s">
+        <v>126</v>
+      </c>
+      <c r="B107">
+        <v>2</v>
+      </c>
+      <c r="C107" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="108" spans="1:3">
+      <c r="A108" t="s">
+        <v>126</v>
+      </c>
+      <c r="B108">
+        <v>3</v>
+      </c>
+      <c r="C108" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="109" spans="1:3">
+      <c r="A109" t="s">
+        <v>126</v>
+      </c>
+      <c r="B109">
+        <v>4</v>
+      </c>
+      <c r="C109" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="110" spans="1:3">
+      <c r="A110" t="s">
+        <v>131</v>
+      </c>
+      <c r="B110">
+        <v>1</v>
+      </c>
+      <c r="C110" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="111" spans="1:3">
+      <c r="A111" t="s">
+        <v>131</v>
+      </c>
+      <c r="B111">
+        <v>2</v>
+      </c>
+      <c r="C111" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="112" spans="1:3">
+      <c r="A112" t="s">
+        <v>131</v>
+      </c>
+      <c r="B112">
+        <v>3</v>
+      </c>
+      <c r="C112" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="113" spans="1:3">
+      <c r="A113" t="s">
+        <v>131</v>
+      </c>
+      <c r="B113">
+        <v>4</v>
+      </c>
+      <c r="C113" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="114" spans="1:3">
+      <c r="A114" t="s">
+        <v>136</v>
+      </c>
+      <c r="B114">
+        <v>1</v>
+      </c>
+      <c r="C114" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="115" spans="1:3">
+      <c r="A115" t="s">
+        <v>136</v>
+      </c>
+      <c r="B115">
+        <v>2</v>
+      </c>
+      <c r="C115" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="116" spans="1:3">
+      <c r="A116" t="s">
+        <v>136</v>
+      </c>
+      <c r="B116">
+        <v>3</v>
+      </c>
+      <c r="C116" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="117" spans="1:3">
+      <c r="A117" t="s">
+        <v>136</v>
+      </c>
+      <c r="B117">
+        <v>4</v>
+      </c>
+      <c r="C117" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="118" spans="1:3">
+      <c r="A118" t="s">
+        <v>141</v>
+      </c>
+      <c r="B118">
+        <v>1</v>
+      </c>
+      <c r="C118" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="119" spans="1:3">
+      <c r="A119" t="s">
+        <v>141</v>
+      </c>
+      <c r="B119">
+        <v>2</v>
+      </c>
+      <c r="C119" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="120" spans="1:3">
+      <c r="A120" t="s">
+        <v>141</v>
+      </c>
+      <c r="B120">
+        <v>3</v>
+      </c>
+      <c r="C120" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="121" spans="1:3">
+      <c r="A121" t="s">
+        <v>141</v>
+      </c>
+      <c r="B121">
+        <v>4</v>
+      </c>
+      <c r="C121" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="122" spans="1:3">
+      <c r="A122" t="s">
+        <v>146</v>
+      </c>
+      <c r="B122">
+        <v>1</v>
+      </c>
+      <c r="C122" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="123" spans="1:3">
+      <c r="A123" t="s">
+        <v>146</v>
+      </c>
+      <c r="B123">
+        <v>2</v>
+      </c>
+      <c r="C123" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="124" spans="1:3">
+      <c r="A124" t="s">
+        <v>146</v>
+      </c>
+      <c r="B124">
+        <v>3</v>
+      </c>
+      <c r="C124" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="125" spans="1:3">
+      <c r="A125" t="s">
+        <v>146</v>
+      </c>
+      <c r="B125">
+        <v>4</v>
+      </c>
+      <c r="C125" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="126" spans="1:3">
+      <c r="A126" t="s">
+        <v>151</v>
+      </c>
+      <c r="B126">
+        <v>1</v>
+      </c>
+      <c r="C126" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="127" spans="1:3">
+      <c r="A127" t="s">
+        <v>151</v>
+      </c>
+      <c r="B127">
+        <v>2</v>
+      </c>
+      <c r="C127" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="128" spans="1:3">
+      <c r="A128" t="s">
+        <v>151</v>
+      </c>
+      <c r="B128">
+        <v>3</v>
+      </c>
+      <c r="C128" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="129" spans="1:3">
+      <c r="A129" t="s">
+        <v>151</v>
+      </c>
+      <c r="B129">
+        <v>4</v>
+      </c>
+      <c r="C129" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="130" spans="1:3">
+      <c r="A130" t="s">
+        <v>156</v>
+      </c>
+      <c r="B130">
+        <v>1</v>
+      </c>
+      <c r="C130" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="131" spans="1:3">
+      <c r="A131" t="s">
+        <v>156</v>
+      </c>
+      <c r="B131">
+        <v>2</v>
+      </c>
+      <c r="C131" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="132" spans="1:3">
+      <c r="A132" t="s">
+        <v>156</v>
+      </c>
+      <c r="B132">
+        <v>3</v>
+      </c>
+      <c r="C132" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="133" spans="1:3">
+      <c r="A133" t="s">
+        <v>156</v>
+      </c>
+      <c r="B133">
+        <v>4</v>
+      </c>
+      <c r="C133" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="134" spans="1:3">
+      <c r="A134" t="s">
+        <v>161</v>
+      </c>
+      <c r="B134">
+        <v>1</v>
+      </c>
+      <c r="C134" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="135" spans="1:3">
+      <c r="A135" t="s">
+        <v>161</v>
+      </c>
+      <c r="B135">
+        <v>2</v>
+      </c>
+      <c r="C135" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="136" spans="1:3">
+      <c r="A136" t="s">
+        <v>161</v>
+      </c>
+      <c r="B136">
+        <v>3</v>
+      </c>
+      <c r="C136" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="137" spans="1:3">
+      <c r="A137" t="s">
+        <v>161</v>
+      </c>
+      <c r="B137">
+        <v>4</v>
+      </c>
+      <c r="C137" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="138" spans="1:3">
+      <c r="A138" t="s">
+        <v>166</v>
+      </c>
+      <c r="B138">
+        <v>1</v>
+      </c>
+      <c r="C138" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="139" spans="1:3">
+      <c r="A139" t="s">
+        <v>166</v>
+      </c>
+      <c r="B139">
+        <v>2</v>
+      </c>
+      <c r="C139" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="140" spans="1:3">
+      <c r="A140" t="s">
+        <v>166</v>
+      </c>
+      <c r="B140">
+        <v>3</v>
+      </c>
+      <c r="C140" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="141" spans="1:3">
+      <c r="A141" t="s">
+        <v>166</v>
+      </c>
+      <c r="B141">
+        <v>4</v>
+      </c>
+      <c r="C141" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="142" spans="1:3">
+      <c r="A142" t="s">
+        <v>171</v>
+      </c>
+      <c r="B142">
+        <v>1</v>
+      </c>
+      <c r="C142" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="143" spans="1:3">
+      <c r="A143" t="s">
+        <v>171</v>
+      </c>
+      <c r="B143">
+        <v>2</v>
+      </c>
+      <c r="C143" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="144" spans="1:3">
+      <c r="A144" t="s">
+        <v>171</v>
+      </c>
+      <c r="B144">
+        <v>3</v>
+      </c>
+      <c r="C144" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="145" spans="1:3">
+      <c r="A145" t="s">
+        <v>171</v>
+      </c>
+      <c r="B145">
+        <v>4</v>
+      </c>
+      <c r="C145" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="146" spans="1:3">
+      <c r="A146" t="s">
+        <v>176</v>
+      </c>
+      <c r="B146">
+        <v>1</v>
+      </c>
+      <c r="C146" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="147" spans="1:3">
+      <c r="A147" t="s">
+        <v>176</v>
+      </c>
+      <c r="B147">
+        <v>2</v>
+      </c>
+      <c r="C147" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="148" spans="1:3">
+      <c r="A148" t="s">
+        <v>176</v>
+      </c>
+      <c r="B148">
+        <v>3</v>
+      </c>
+      <c r="C148" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="149" spans="1:3">
+      <c r="A149" t="s">
+        <v>176</v>
+      </c>
+      <c r="B149">
+        <v>4</v>
+      </c>
+      <c r="C149" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="150" spans="1:3">
+      <c r="A150" t="s">
+        <v>181</v>
+      </c>
+      <c r="B150">
+        <v>1</v>
+      </c>
+      <c r="C150" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="151" spans="1:3">
+      <c r="A151" t="s">
+        <v>181</v>
+      </c>
+      <c r="B151">
+        <v>2</v>
+      </c>
+      <c r="C151" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="152" spans="1:3">
+      <c r="A152" t="s">
+        <v>181</v>
+      </c>
+      <c r="B152">
+        <v>3</v>
+      </c>
+      <c r="C152" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="153" spans="1:3">
+      <c r="A153" t="s">
+        <v>181</v>
+      </c>
+      <c r="B153">
+        <v>4</v>
+      </c>
+      <c r="C153" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="154" spans="1:3">
+      <c r="A154" t="s">
+        <v>186</v>
+      </c>
+      <c r="B154">
+        <v>1</v>
+      </c>
+      <c r="C154" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="155" spans="1:3">
+      <c r="A155" t="s">
+        <v>186</v>
+      </c>
+      <c r="B155">
+        <v>2</v>
+      </c>
+      <c r="C155" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="156" spans="1:3">
+      <c r="A156" t="s">
+        <v>186</v>
+      </c>
+      <c r="B156">
+        <v>3</v>
+      </c>
+      <c r="C156" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="157" spans="1:3">
+      <c r="A157" t="s">
+        <v>186</v>
+      </c>
+      <c r="B157">
+        <v>4</v>
+      </c>
+      <c r="C157" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="158" spans="1:3">
+      <c r="A158" t="s">
+        <v>191</v>
+      </c>
+      <c r="B158">
+        <v>1</v>
+      </c>
+      <c r="C158" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="159" spans="1:3">
+      <c r="A159" t="s">
+        <v>191</v>
+      </c>
+      <c r="B159">
+        <v>2</v>
+      </c>
+      <c r="C159" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="160" spans="1:3">
+      <c r="A160" t="s">
+        <v>191</v>
+      </c>
+      <c r="B160">
+        <v>3</v>
+      </c>
+      <c r="C160" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="161" spans="1:3">
+      <c r="A161" t="s">
+        <v>191</v>
+      </c>
+      <c r="B161">
+        <v>4</v>
+      </c>
+      <c r="C161" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="162" spans="1:3">
+      <c r="A162" t="s">
+        <v>196</v>
+      </c>
+      <c r="B162">
+        <v>1</v>
+      </c>
+      <c r="C162" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="163" spans="1:3">
+      <c r="A163" t="s">
+        <v>196</v>
+      </c>
+      <c r="B163">
+        <v>2</v>
+      </c>
+      <c r="C163" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="164" spans="1:3">
+      <c r="A164" t="s">
+        <v>196</v>
+      </c>
+      <c r="B164">
+        <v>3</v>
+      </c>
+      <c r="C164" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="165" spans="1:3">
+      <c r="A165" t="s">
+        <v>196</v>
+      </c>
+      <c r="B165">
+        <v>4</v>
+      </c>
+      <c r="C165" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="166" spans="1:3">
+      <c r="A166" t="s">
+        <v>201</v>
+      </c>
+      <c r="B166">
+        <v>1</v>
+      </c>
+      <c r="C166" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="167" spans="1:3">
+      <c r="A167" t="s">
+        <v>201</v>
+      </c>
+      <c r="B167">
+        <v>2</v>
+      </c>
+      <c r="C167" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="168" spans="1:3">
+      <c r="A168" t="s">
+        <v>201</v>
+      </c>
+      <c r="B168">
+        <v>3</v>
+      </c>
+      <c r="C168" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="169" spans="1:3">
+      <c r="A169" t="s">
+        <v>201</v>
+      </c>
+      <c r="B169">
+        <v>4</v>
+      </c>
+      <c r="C169" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="170" spans="1:3">
+      <c r="A170" t="s">
+        <v>206</v>
+      </c>
+      <c r="B170">
+        <v>1</v>
+      </c>
+      <c r="C170" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="171" spans="1:3">
+      <c r="A171" t="s">
+        <v>206</v>
+      </c>
+      <c r="B171">
+        <v>2</v>
+      </c>
+      <c r="C171" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="172" spans="1:3">
+      <c r="A172" t="s">
+        <v>206</v>
+      </c>
+      <c r="B172">
+        <v>3</v>
+      </c>
+      <c r="C172" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="173" spans="1:3">
+      <c r="A173" t="s">
+        <v>206</v>
+      </c>
+      <c r="B173">
+        <v>4</v>
+      </c>
+      <c r="C173" t="s">
+        <v>210</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>

--- a/data/情景交代.xlsx
+++ b/data/情景交代.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="21997" windowHeight="9855"/>
+    <workbookView windowWidth="22192" windowHeight="10387"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="347" uniqueCount="211">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="339" uniqueCount="210">
   <si>
     <t>疾病</t>
   </si>
@@ -344,7 +344,7 @@
     <t>患者行颈椎肿瘤切除内固定+肋骨肿瘤切除术，术后症状好转。病理确诊肺来源转移性腺癌。家属咨询后续治疗方案。请你向家属解释后续治疗（化疗、靶向等）及预后。</t>
   </si>
   <si>
-    <t>“脑中风的警报”</t>
+    <t>“半身风云”</t>
   </si>
   <si>
     <t>张大爷，68岁，有高血压史，晨起突然出现右侧肢体无力、麻木，言语不清，口角左偏。急诊头颅CT未见出血，考虑急性缺血性脑卒中。你是接诊医生，请开始问诊。</t>
@@ -357,9 +357,6 @@
   </si>
   <si>
     <t>出院前患者右侧肢体肌力恢复至4级，言语清晰。需指导二级预防药物（阿司匹林、他汀）、生活方式调整及定期随访。请你进行出院宣教。</t>
-  </si>
-  <si>
-    <t>“半身风云”</t>
   </si>
   <si>
     <t>“惊厥之舞”</t>
@@ -1804,7 +1801,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:C173"/>
+  <dimension ref="A1:C169"/>
   <sheetFormatPr defaultColWidth="9.02654867256637" defaultRowHeight="13.5" outlineLevelCol="2"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -2794,7 +2791,7 @@
         <v>1</v>
       </c>
       <c r="C90" t="s">
-        <v>106</v>
+        <v>111</v>
       </c>
     </row>
     <row r="91" spans="1:3">
@@ -2805,7 +2802,7 @@
         <v>2</v>
       </c>
       <c r="C91" t="s">
-        <v>107</v>
+        <v>112</v>
       </c>
     </row>
     <row r="92" spans="1:3">
@@ -2816,7 +2813,7 @@
         <v>3</v>
       </c>
       <c r="C92" t="s">
-        <v>108</v>
+        <v>113</v>
       </c>
     </row>
     <row r="93" spans="1:3">
@@ -2827,887 +2824,843 @@
         <v>4</v>
       </c>
       <c r="C93" t="s">
-        <v>109</v>
+        <v>114</v>
       </c>
     </row>
     <row r="94" spans="1:3">
       <c r="A94" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="B94">
         <v>1</v>
       </c>
       <c r="C94" t="s">
-        <v>112</v>
+        <v>116</v>
       </c>
     </row>
     <row r="95" spans="1:3">
       <c r="A95" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="B95">
         <v>2</v>
       </c>
       <c r="C95" t="s">
-        <v>113</v>
+        <v>117</v>
       </c>
     </row>
     <row r="96" spans="1:3">
       <c r="A96" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="B96">
         <v>3</v>
       </c>
       <c r="C96" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
     </row>
     <row r="97" spans="1:3">
       <c r="A97" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="B97">
         <v>4</v>
       </c>
       <c r="C97" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
     </row>
     <row r="98" spans="1:3">
       <c r="A98" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="B98">
         <v>1</v>
       </c>
       <c r="C98" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
     </row>
     <row r="99" spans="1:3">
       <c r="A99" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="B99">
         <v>2</v>
       </c>
       <c r="C99" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
     </row>
     <row r="100" spans="1:3">
       <c r="A100" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="B100">
         <v>3</v>
       </c>
       <c r="C100" t="s">
-        <v>119</v>
+        <v>123</v>
       </c>
     </row>
     <row r="101" spans="1:3">
       <c r="A101" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="B101">
         <v>4</v>
       </c>
       <c r="C101" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
     </row>
     <row r="102" spans="1:3">
       <c r="A102" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="B102">
         <v>1</v>
       </c>
       <c r="C102" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
     </row>
     <row r="103" spans="1:3">
       <c r="A103" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="B103">
         <v>2</v>
       </c>
       <c r="C103" t="s">
-        <v>123</v>
+        <v>127</v>
       </c>
     </row>
     <row r="104" spans="1:3">
       <c r="A104" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="B104">
         <v>3</v>
       </c>
       <c r="C104" t="s">
-        <v>124</v>
+        <v>128</v>
       </c>
     </row>
     <row r="105" spans="1:3">
       <c r="A105" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="B105">
         <v>4</v>
       </c>
       <c r="C105" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
     </row>
     <row r="106" spans="1:3">
       <c r="A106" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="B106">
         <v>1</v>
       </c>
       <c r="C106" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
     </row>
     <row r="107" spans="1:3">
       <c r="A107" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="B107">
         <v>2</v>
       </c>
       <c r="C107" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
     </row>
     <row r="108" spans="1:3">
       <c r="A108" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="B108">
         <v>3</v>
       </c>
       <c r="C108" t="s">
-        <v>129</v>
+        <v>133</v>
       </c>
     </row>
     <row r="109" spans="1:3">
       <c r="A109" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="B109">
         <v>4</v>
       </c>
       <c r="C109" t="s">
-        <v>130</v>
+        <v>134</v>
       </c>
     </row>
     <row r="110" spans="1:3">
       <c r="A110" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="B110">
         <v>1</v>
       </c>
       <c r="C110" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
     </row>
     <row r="111" spans="1:3">
       <c r="A111" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="B111">
         <v>2</v>
       </c>
       <c r="C111" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
     </row>
     <row r="112" spans="1:3">
       <c r="A112" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="B112">
         <v>3</v>
       </c>
       <c r="C112" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
     </row>
     <row r="113" spans="1:3">
       <c r="A113" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="B113">
         <v>4</v>
       </c>
       <c r="C113" t="s">
-        <v>135</v>
+        <v>139</v>
       </c>
     </row>
     <row r="114" spans="1:3">
       <c r="A114" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="B114">
         <v>1</v>
       </c>
       <c r="C114" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
     </row>
     <row r="115" spans="1:3">
       <c r="A115" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="B115">
         <v>2</v>
       </c>
       <c r="C115" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
     </row>
     <row r="116" spans="1:3">
       <c r="A116" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="B116">
         <v>3</v>
       </c>
       <c r="C116" t="s">
-        <v>139</v>
+        <v>143</v>
       </c>
     </row>
     <row r="117" spans="1:3">
       <c r="A117" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="B117">
         <v>4</v>
       </c>
       <c r="C117" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
     </row>
     <row r="118" spans="1:3">
       <c r="A118" t="s">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="B118">
         <v>1</v>
       </c>
       <c r="C118" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
     </row>
     <row r="119" spans="1:3">
       <c r="A119" t="s">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="B119">
         <v>2</v>
       </c>
       <c r="C119" t="s">
-        <v>143</v>
+        <v>147</v>
       </c>
     </row>
     <row r="120" spans="1:3">
       <c r="A120" t="s">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="B120">
         <v>3</v>
       </c>
       <c r="C120" t="s">
-        <v>144</v>
+        <v>148</v>
       </c>
     </row>
     <row r="121" spans="1:3">
       <c r="A121" t="s">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="B121">
         <v>4</v>
       </c>
       <c r="C121" t="s">
-        <v>145</v>
+        <v>149</v>
       </c>
     </row>
     <row r="122" spans="1:3">
       <c r="A122" t="s">
-        <v>146</v>
+        <v>150</v>
       </c>
       <c r="B122">
         <v>1</v>
       </c>
       <c r="C122" t="s">
-        <v>147</v>
+        <v>151</v>
       </c>
     </row>
     <row r="123" spans="1:3">
       <c r="A123" t="s">
-        <v>146</v>
+        <v>150</v>
       </c>
       <c r="B123">
         <v>2</v>
       </c>
       <c r="C123" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
     </row>
     <row r="124" spans="1:3">
       <c r="A124" t="s">
-        <v>146</v>
+        <v>150</v>
       </c>
       <c r="B124">
         <v>3</v>
       </c>
       <c r="C124" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
     </row>
     <row r="125" spans="1:3">
       <c r="A125" t="s">
-        <v>146</v>
+        <v>150</v>
       </c>
       <c r="B125">
         <v>4</v>
       </c>
       <c r="C125" t="s">
-        <v>150</v>
+        <v>154</v>
       </c>
     </row>
     <row r="126" spans="1:3">
       <c r="A126" t="s">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="B126">
         <v>1</v>
       </c>
       <c r="C126" t="s">
-        <v>152</v>
+        <v>156</v>
       </c>
     </row>
     <row r="127" spans="1:3">
       <c r="A127" t="s">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="B127">
         <v>2</v>
       </c>
       <c r="C127" t="s">
-        <v>153</v>
+        <v>157</v>
       </c>
     </row>
     <row r="128" spans="1:3">
       <c r="A128" t="s">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="B128">
         <v>3</v>
       </c>
       <c r="C128" t="s">
-        <v>154</v>
+        <v>158</v>
       </c>
     </row>
     <row r="129" spans="1:3">
       <c r="A129" t="s">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="B129">
         <v>4</v>
       </c>
       <c r="C129" t="s">
-        <v>155</v>
+        <v>159</v>
       </c>
     </row>
     <row r="130" spans="1:3">
       <c r="A130" t="s">
-        <v>156</v>
+        <v>160</v>
       </c>
       <c r="B130">
         <v>1</v>
       </c>
       <c r="C130" t="s">
-        <v>157</v>
+        <v>161</v>
       </c>
     </row>
     <row r="131" spans="1:3">
       <c r="A131" t="s">
-        <v>156</v>
+        <v>160</v>
       </c>
       <c r="B131">
         <v>2</v>
       </c>
       <c r="C131" t="s">
-        <v>158</v>
+        <v>162</v>
       </c>
     </row>
     <row r="132" spans="1:3">
       <c r="A132" t="s">
-        <v>156</v>
+        <v>160</v>
       </c>
       <c r="B132">
         <v>3</v>
       </c>
       <c r="C132" t="s">
-        <v>159</v>
+        <v>163</v>
       </c>
     </row>
     <row r="133" spans="1:3">
       <c r="A133" t="s">
-        <v>156</v>
+        <v>160</v>
       </c>
       <c r="B133">
         <v>4</v>
       </c>
       <c r="C133" t="s">
-        <v>160</v>
+        <v>164</v>
       </c>
     </row>
     <row r="134" spans="1:3">
       <c r="A134" t="s">
-        <v>161</v>
+        <v>165</v>
       </c>
       <c r="B134">
         <v>1</v>
       </c>
       <c r="C134" t="s">
-        <v>162</v>
+        <v>166</v>
       </c>
     </row>
     <row r="135" spans="1:3">
       <c r="A135" t="s">
-        <v>161</v>
+        <v>165</v>
       </c>
       <c r="B135">
         <v>2</v>
       </c>
       <c r="C135" t="s">
-        <v>163</v>
+        <v>167</v>
       </c>
     </row>
     <row r="136" spans="1:3">
       <c r="A136" t="s">
-        <v>161</v>
+        <v>165</v>
       </c>
       <c r="B136">
         <v>3</v>
       </c>
       <c r="C136" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
     </row>
     <row r="137" spans="1:3">
       <c r="A137" t="s">
-        <v>161</v>
+        <v>165</v>
       </c>
       <c r="B137">
         <v>4</v>
       </c>
       <c r="C137" t="s">
-        <v>165</v>
+        <v>169</v>
       </c>
     </row>
     <row r="138" spans="1:3">
       <c r="A138" t="s">
-        <v>166</v>
+        <v>170</v>
       </c>
       <c r="B138">
         <v>1</v>
       </c>
       <c r="C138" t="s">
-        <v>167</v>
+        <v>171</v>
       </c>
     </row>
     <row r="139" spans="1:3">
       <c r="A139" t="s">
-        <v>166</v>
+        <v>170</v>
       </c>
       <c r="B139">
         <v>2</v>
       </c>
       <c r="C139" t="s">
-        <v>168</v>
+        <v>172</v>
       </c>
     </row>
     <row r="140" spans="1:3">
       <c r="A140" t="s">
-        <v>166</v>
+        <v>170</v>
       </c>
       <c r="B140">
         <v>3</v>
       </c>
       <c r="C140" t="s">
-        <v>169</v>
+        <v>173</v>
       </c>
     </row>
     <row r="141" spans="1:3">
       <c r="A141" t="s">
-        <v>166</v>
+        <v>170</v>
       </c>
       <c r="B141">
         <v>4</v>
       </c>
       <c r="C141" t="s">
-        <v>170</v>
+        <v>174</v>
       </c>
     </row>
     <row r="142" spans="1:3">
       <c r="A142" t="s">
-        <v>171</v>
+        <v>175</v>
       </c>
       <c r="B142">
         <v>1</v>
       </c>
       <c r="C142" t="s">
-        <v>172</v>
+        <v>176</v>
       </c>
     </row>
     <row r="143" spans="1:3">
       <c r="A143" t="s">
-        <v>171</v>
+        <v>175</v>
       </c>
       <c r="B143">
         <v>2</v>
       </c>
       <c r="C143" t="s">
-        <v>173</v>
+        <v>177</v>
       </c>
     </row>
     <row r="144" spans="1:3">
       <c r="A144" t="s">
-        <v>171</v>
+        <v>175</v>
       </c>
       <c r="B144">
         <v>3</v>
       </c>
       <c r="C144" t="s">
-        <v>174</v>
+        <v>178</v>
       </c>
     </row>
     <row r="145" spans="1:3">
       <c r="A145" t="s">
-        <v>171</v>
+        <v>175</v>
       </c>
       <c r="B145">
         <v>4</v>
       </c>
       <c r="C145" t="s">
-        <v>175</v>
+        <v>179</v>
       </c>
     </row>
     <row r="146" spans="1:3">
       <c r="A146" t="s">
-        <v>176</v>
+        <v>180</v>
       </c>
       <c r="B146">
         <v>1</v>
       </c>
       <c r="C146" t="s">
-        <v>177</v>
+        <v>181</v>
       </c>
     </row>
     <row r="147" spans="1:3">
       <c r="A147" t="s">
-        <v>176</v>
+        <v>180</v>
       </c>
       <c r="B147">
         <v>2</v>
       </c>
       <c r="C147" t="s">
-        <v>178</v>
+        <v>182</v>
       </c>
     </row>
     <row r="148" spans="1:3">
       <c r="A148" t="s">
-        <v>176</v>
+        <v>180</v>
       </c>
       <c r="B148">
         <v>3</v>
       </c>
       <c r="C148" t="s">
-        <v>179</v>
+        <v>183</v>
       </c>
     </row>
     <row r="149" spans="1:3">
       <c r="A149" t="s">
-        <v>176</v>
+        <v>180</v>
       </c>
       <c r="B149">
         <v>4</v>
       </c>
       <c r="C149" t="s">
-        <v>180</v>
+        <v>184</v>
       </c>
     </row>
     <row r="150" spans="1:3">
       <c r="A150" t="s">
-        <v>181</v>
+        <v>185</v>
       </c>
       <c r="B150">
         <v>1</v>
       </c>
       <c r="C150" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
     </row>
     <row r="151" spans="1:3">
       <c r="A151" t="s">
-        <v>181</v>
+        <v>185</v>
       </c>
       <c r="B151">
         <v>2</v>
       </c>
       <c r="C151" t="s">
-        <v>183</v>
+        <v>187</v>
       </c>
     </row>
     <row r="152" spans="1:3">
       <c r="A152" t="s">
-        <v>181</v>
+        <v>185</v>
       </c>
       <c r="B152">
         <v>3</v>
       </c>
       <c r="C152" t="s">
-        <v>184</v>
+        <v>188</v>
       </c>
     </row>
     <row r="153" spans="1:3">
       <c r="A153" t="s">
-        <v>181</v>
+        <v>185</v>
       </c>
       <c r="B153">
         <v>4</v>
       </c>
       <c r="C153" t="s">
-        <v>185</v>
+        <v>189</v>
       </c>
     </row>
     <row r="154" spans="1:3">
       <c r="A154" t="s">
-        <v>186</v>
+        <v>190</v>
       </c>
       <c r="B154">
         <v>1</v>
       </c>
       <c r="C154" t="s">
-        <v>187</v>
+        <v>191</v>
       </c>
     </row>
     <row r="155" spans="1:3">
       <c r="A155" t="s">
-        <v>186</v>
+        <v>190</v>
       </c>
       <c r="B155">
         <v>2</v>
       </c>
       <c r="C155" t="s">
-        <v>188</v>
+        <v>192</v>
       </c>
     </row>
     <row r="156" spans="1:3">
       <c r="A156" t="s">
-        <v>186</v>
+        <v>190</v>
       </c>
       <c r="B156">
         <v>3</v>
       </c>
       <c r="C156" t="s">
-        <v>189</v>
+        <v>193</v>
       </c>
     </row>
     <row r="157" spans="1:3">
       <c r="A157" t="s">
-        <v>186</v>
+        <v>190</v>
       </c>
       <c r="B157">
         <v>4</v>
       </c>
       <c r="C157" t="s">
-        <v>190</v>
+        <v>194</v>
       </c>
     </row>
     <row r="158" spans="1:3">
       <c r="A158" t="s">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="B158">
         <v>1</v>
       </c>
       <c r="C158" t="s">
-        <v>192</v>
+        <v>196</v>
       </c>
     </row>
     <row r="159" spans="1:3">
       <c r="A159" t="s">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="B159">
         <v>2</v>
       </c>
       <c r="C159" t="s">
-        <v>193</v>
+        <v>197</v>
       </c>
     </row>
     <row r="160" spans="1:3">
       <c r="A160" t="s">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="B160">
         <v>3</v>
       </c>
       <c r="C160" t="s">
-        <v>194</v>
+        <v>198</v>
       </c>
     </row>
     <row r="161" spans="1:3">
       <c r="A161" t="s">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="B161">
         <v>4</v>
       </c>
       <c r="C161" t="s">
-        <v>195</v>
+        <v>199</v>
       </c>
     </row>
     <row r="162" spans="1:3">
       <c r="A162" t="s">
-        <v>196</v>
+        <v>200</v>
       </c>
       <c r="B162">
         <v>1</v>
       </c>
       <c r="C162" t="s">
-        <v>197</v>
+        <v>201</v>
       </c>
     </row>
     <row r="163" spans="1:3">
       <c r="A163" t="s">
-        <v>196</v>
+        <v>200</v>
       </c>
       <c r="B163">
         <v>2</v>
       </c>
       <c r="C163" t="s">
-        <v>198</v>
+        <v>202</v>
       </c>
     </row>
     <row r="164" spans="1:3">
       <c r="A164" t="s">
-        <v>196</v>
+        <v>200</v>
       </c>
       <c r="B164">
         <v>3</v>
       </c>
       <c r="C164" t="s">
-        <v>199</v>
+        <v>203</v>
       </c>
     </row>
     <row r="165" spans="1:3">
       <c r="A165" t="s">
-        <v>196</v>
+        <v>200</v>
       </c>
       <c r="B165">
         <v>4</v>
       </c>
       <c r="C165" t="s">
-        <v>200</v>
+        <v>204</v>
       </c>
     </row>
     <row r="166" spans="1:3">
       <c r="A166" t="s">
-        <v>201</v>
+        <v>205</v>
       </c>
       <c r="B166">
         <v>1</v>
       </c>
       <c r="C166" t="s">
-        <v>202</v>
+        <v>206</v>
       </c>
     </row>
     <row r="167" spans="1:3">
       <c r="A167" t="s">
-        <v>201</v>
+        <v>205</v>
       </c>
       <c r="B167">
         <v>2</v>
       </c>
       <c r="C167" t="s">
-        <v>203</v>
+        <v>207</v>
       </c>
     </row>
     <row r="168" spans="1:3">
       <c r="A168" t="s">
-        <v>201</v>
+        <v>205</v>
       </c>
       <c r="B168">
         <v>3</v>
       </c>
       <c r="C168" t="s">
-        <v>204</v>
+        <v>208</v>
       </c>
     </row>
     <row r="169" spans="1:3">
       <c r="A169" t="s">
-        <v>201</v>
+        <v>205</v>
       </c>
       <c r="B169">
         <v>4</v>
       </c>
       <c r="C169" t="s">
-        <v>205</v>
-      </c>
-    </row>
-    <row r="170" spans="1:3">
-      <c r="A170" t="s">
-        <v>206</v>
-      </c>
-      <c r="B170">
-        <v>1</v>
-      </c>
-      <c r="C170" t="s">
-        <v>207</v>
-      </c>
-    </row>
-    <row r="171" spans="1:3">
-      <c r="A171" t="s">
-        <v>206</v>
-      </c>
-      <c r="B171">
-        <v>2</v>
-      </c>
-      <c r="C171" t="s">
-        <v>208</v>
-      </c>
-    </row>
-    <row r="172" spans="1:3">
-      <c r="A172" t="s">
-        <v>206</v>
-      </c>
-      <c r="B172">
-        <v>3</v>
-      </c>
-      <c r="C172" t="s">
         <v>209</v>
-      </c>
-    </row>
-    <row r="173" spans="1:3">
-      <c r="A173" t="s">
-        <v>206</v>
-      </c>
-      <c r="B173">
-        <v>4</v>
-      </c>
-      <c r="C173" t="s">
-        <v>210</v>
       </c>
     </row>
   </sheetData>
